--- a/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor</t>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,51; 54,01</t>
+          <t>20,13; 56,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 39,72</t>
+          <t>12,7; 39,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 39,96</t>
+          <t>18,96; 40,0</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,79; 45,98</t>
+          <t>22,86; 46,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,51; 43,2</t>
+          <t>20,38; 43,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,43; 40,29</t>
+          <t>24,56; 40,74</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,24; 63,58</t>
+          <t>35,8; 63,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,52; 47,24</t>
+          <t>22,84; 47,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,12; 51,22</t>
+          <t>32,09; 50,99</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 38,03</t>
+          <t>7,92; 36,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,64; 47,08</t>
+          <t>23,55; 47,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,13; 37,26</t>
+          <t>15,25; 37,54</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,31; 40,24</t>
+          <t>18,84; 40,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,86; 39,1</t>
+          <t>26,39; 39,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,16; 36,15</t>
+          <t>23,81; 36,94</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11171</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3300; 9298</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2840; 8930</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7348; 15501</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15578</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15190</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30767</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10660; 21594</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9981; 21296</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23480; 38947</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>18890</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15638</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34528</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>13301; 23624</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10543; 21913</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26740; 42487</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>16625</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22483</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39107</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6273; 28976</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>15356; 30881</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22015; 54203</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>57005</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>115574</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33793; 72844</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>48224; 71335</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>86219; 133730</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 56,73</t>
+          <t>19,17; 54,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,7; 39,94</t>
+          <t>12,82; 38,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,96; 40,0</t>
+          <t>18,61; 41,59</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,86; 46,32</t>
+          <t>22,08; 44,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,38; 43,48</t>
+          <t>21,24; 42,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,56; 40,74</t>
+          <t>24,27; 40,45</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,8; 63,59</t>
+          <t>37,65; 64,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,84; 47,46</t>
+          <t>21,4; 47,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,09; 50,99</t>
+          <t>33,2; 51,66</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 36,59</t>
+          <t>6,38; 36,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,55; 47,36</t>
+          <t>22,38; 46,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 37,54</t>
+          <t>15,45; 37,41</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 40,62</t>
+          <t>19,91; 40,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,39; 39,04</t>
+          <t>26,16; 38,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,81; 36,94</t>
+          <t>24,88; 37,03</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3300; 9298</t>
+          <t>3142; 8957</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2840; 8930</t>
+          <t>2866; 8594</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7348; 15501</t>
+          <t>7212; 16114</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10660; 21594</t>
+          <t>10294; 20789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9981; 21296</t>
+          <t>10405; 21042</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23480; 38947</t>
+          <t>23203; 38675</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13301; 23624</t>
+          <t>13988; 23777</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10543; 21913</t>
+          <t>9881; 22130</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26740; 42487</t>
+          <t>27661; 43047</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6273; 28976</t>
+          <t>5049; 28882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15356; 30881</t>
+          <t>14593; 30278</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22015; 54203</t>
+          <t>22308; 54020</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33793; 72844</t>
+          <t>35717; 73114</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48224; 71335</t>
+          <t>47794; 69961</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86219; 133730</t>
+          <t>90094; 134078</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,17; 54,65</t>
+          <t>12,59; 40,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 38,44</t>
+          <t>21,29; 55,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,61; 41,59</t>
+          <t>20,18; 41,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,08; 44,59</t>
+          <t>20,13; 42,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,24; 42,96</t>
+          <t>23,94; 47,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,27; 40,45</t>
+          <t>25,49; 40,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,65; 64,0</t>
+          <t>22,45; 46,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,4; 47,93</t>
+          <t>36,04; 63,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 51,66</t>
+          <t>31,47; 51,48</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 36,47</t>
+          <t>22,3; 46,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,38; 46,44</t>
+          <t>23,17; 45,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 37,41</t>
+          <t>25,23; 42,47</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 40,77</t>
+          <t>25,79; 38,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,16; 38,29</t>
+          <t>32,78; 45,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,88; 37,03</t>
+          <t>30,14; 39,27</t>
         </is>
       </c>
     </row>
@@ -825,18 +825,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>9427</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3142; 8957</t>
+          <t>2194; 7062</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2866; 8594</t>
+          <t>3082; 7976</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7212; 16114</t>
+          <t>6440; 13204</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>26966</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10294; 20789</t>
+          <t>8302; 17513</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10405; 21042</t>
+          <t>9791; 19375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23203; 38675</t>
+          <t>20939; 33644</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34396</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13988; 23777</t>
+          <t>9873; 20595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9881; 22130</t>
+          <t>13675; 24195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27661; 43047</t>
+          <t>25781; 42169</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22483</t>
+          <t>17068</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39107</t>
+          <t>38268</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5049; 28882</t>
+          <t>14012; 29280</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14593; 30278</t>
+          <t>11889; 23284</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22308; 54020</t>
+          <t>28798; 48488</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35717; 73114</t>
+          <t>42683; 63754</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47794; 69961</t>
+          <t>47419; 66158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90094; 134078</t>
+          <t>93456; 121778</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>36,92%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,59; 40,51</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>21,29; 55,1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20,18; 41,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34,91%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>20,13; 42,47</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23,94; 47,38</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25,49; 40,96</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>33,84%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>51,42%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>22,45; 46,84</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36,04; 63,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31,47; 51,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>33,74%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>33,26%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>22,3; 46,59</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>23,17; 45,37</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25,23; 42,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>25,79; 38,53</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32,78; 45,74</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>30,14; 39,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2341470054753309</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.3691802310950328</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2954101722034155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4082</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5345</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9427</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.125863479048055</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.212920471618641</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2018160158899237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2194; 7062</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3082; 7976</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6440; 13204</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4051075366143772</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5509654285606167</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.413790308737988</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3077019457751233</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3491246487137399</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3283277933795068</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12688</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14278</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26966</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2013386941944556</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.2394112431219355</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.2549472910495186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8302; 17513</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9791; 19375</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>20939; 33644</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4247012129885673</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4737640490575458</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4096322744889379</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3384464872065585</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.514228515222818</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4198749975807776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>14882</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>19514</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34396</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2245305782116942</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3603660343162438</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3147145589402178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9873; 20595</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13675; 24195</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>25781; 42169</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4683817116623025</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6375819510684673</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.514766921838867</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3373665342904275</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3325708519200798</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.3352106586525249</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>21200</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17068</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38268</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.2229809859516407</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.2316700484868443</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.2522569760169201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>14012; 29280</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11889; 23284</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>28798; 48488</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4659466812728387</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4537013373225383</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4247342315971847</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.3193876990993028</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3885750505526774</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3516569265573155</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>52852</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>56204</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>109056</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.2579387873970066</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.3278366154360199</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.301353385107934</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>42683; 63754</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>47419; 66158</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>93456; 121778</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3852719095209731</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4573913188523958</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3926786971843211</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>4082</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>5345</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9427</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2194</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>3082</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6440</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7062</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7976</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>13204</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>12688</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>14278</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>26966</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>8302</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>9791</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>20939</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>17513</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>19375</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>33644</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>14882</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>19514</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>34396</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>9873</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>13675</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>25781</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>20595</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>24195</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>42169</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>21200</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>17068</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>38268</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>14012</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>11889</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>28798</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>29280</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>23284</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>48488</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>52852</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>56204</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>109056</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>42683</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>47419</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>93456</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>63754</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>66158</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>121778</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>